--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/pre LAM_HRM-2031-0292/Panel 7/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/pre LAM_HRM-2031-0292/Panel 7/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.98172</v>
+        <v>17.07233</v>
       </c>
       <c r="D2" t="n">
-        <v>16.37012</v>
+        <v>16.41291</v>
       </c>
       <c r="E2" t="n">
-        <v>16.78028</v>
+        <v>16.63527</v>
       </c>
       <c r="F2" t="n">
-        <v>42.54908</v>
+        <v>42.36568</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05056</v>
+        <v>0.05148</v>
       </c>
       <c r="H2" t="n">
-        <v>1.83476</v>
+        <v>1.80192</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.72122</v>
+        <v>17.13741</v>
       </c>
       <c r="D3" t="n">
-        <v>16.35589</v>
+        <v>16.4134</v>
       </c>
       <c r="E3" t="n">
-        <v>16.98949</v>
+        <v>16.74801</v>
       </c>
       <c r="F3" t="n">
-        <v>42.59789</v>
+        <v>42.13411</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04994</v>
+        <v>0.05091</v>
       </c>
       <c r="H3" t="n">
-        <v>1.82538</v>
+        <v>1.80328</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.72347</v>
+        <v>16.69337</v>
       </c>
       <c r="D4" t="n">
-        <v>16.91874</v>
+        <v>16.53776</v>
       </c>
       <c r="E4" t="n">
-        <v>16.51001</v>
+        <v>16.64084</v>
       </c>
       <c r="F4" t="n">
-        <v>43.13172</v>
+        <v>42.49505</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0513</v>
+        <v>0.05057</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82101</v>
+        <v>1.83082</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.56156</v>
+        <v>16.84965</v>
       </c>
       <c r="D6" t="n">
-        <v>16.1984</v>
+        <v>16.02293</v>
       </c>
       <c r="E6" t="n">
-        <v>16.59502</v>
+        <v>16.1274</v>
       </c>
       <c r="F6" t="n">
-        <v>21.48033</v>
+        <v>21.6874</v>
       </c>
       <c r="G6" t="n">
-        <v>34.57949</v>
+        <v>33.47673</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.96436</v>
+        <v>16.57017</v>
       </c>
       <c r="D7" t="n">
-        <v>15.83085</v>
+        <v>16.02737</v>
       </c>
       <c r="E7" t="n">
-        <v>16.24884</v>
+        <v>16.26492</v>
       </c>
       <c r="F7" t="n">
-        <v>21.34901</v>
+        <v>21.94588</v>
       </c>
       <c r="G7" t="n">
-        <v>34.4243</v>
+        <v>33.27919</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.76493</v>
+        <v>16.65459</v>
       </c>
       <c r="D8" t="n">
-        <v>15.68428</v>
+        <v>16.37799</v>
       </c>
       <c r="E8" t="n">
-        <v>16.40605</v>
+        <v>16.46123</v>
       </c>
       <c r="F8" t="n">
-        <v>21.6257</v>
+        <v>21.3462</v>
       </c>
       <c r="G8" t="n">
-        <v>34.20462</v>
+        <v>34.32621</v>
       </c>
     </row>
   </sheetData>
